--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
@@ -735,14 +735,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2891
+</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
@@ -750,44 +755,39 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -826,7 +826,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
@@ -838,12 +838,12 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>132</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -877,7 +877,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4645
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>2651</t>
@@ -885,7 +890,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -925,7 +930,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -938,36 +943,38 @@
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">77
+990
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -997,13 +1004,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -1022,13 +1029,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1044,16 +1051,12 @@
 </t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">12
@@ -1062,13 +1065,13 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1079,30 +1082,29 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">042
-</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">942
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
+          <t>217</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">179
 </t>
@@ -1110,7 +1112,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1128,7 +1130,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
@@ -1138,19 +1140,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">9310
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1169,7 +1171,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552
+          <t xml:space="preserve">3552
 </t>
         </is>
       </c>
@@ -1191,56 +1193,59 @@
 </t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">017
-</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">771
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1252,7 +1257,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1264,13 +1269,13 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1280,27 +1285,27 @@
 </t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="X7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">813
+      <c r="W7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3279
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1337,62 +1342,60 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3189
+          <t xml:space="preserve">27219
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1410,13 +1413,13 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1432,9 +1435,9 @@
 </t>
         </is>
       </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+      <c r="X8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -1446,7 +1449,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -1466,7 +1469,8 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1482,43 +1486,51 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">1342
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>616</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n"/>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -1531,13 +1543,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">8929
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">056
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
@@ -1561,7 +1573,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -1573,7 +1585,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1589,31 +1601,29 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
+      <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>550</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1623,13 +1633,13 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1646,63 +1656,67 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="3" t="n"/>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6379
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">430
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">914
-</t>
+          <t xml:space="preserve">541
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>09</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="X10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
@@ -1714,7 +1728,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1733,113 +1747,127 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n"/>
+          <t xml:space="preserve">77871
+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2531
+228548177
+</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1975
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>017</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">986
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1855,67 +1883,63 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>041</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">789
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">277275
+163
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1925,21 +1949,21 @@
 </t>
         </is>
       </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1957,25 +1981,24 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">8850
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1994,19 +2017,20 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -2017,63 +2041,58 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">001
+</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>447</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -2082,16 +2101,16 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">668
@@ -2100,7 +2119,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
@@ -2118,17 +2137,22 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -2145,7 +2169,7 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2157,117 +2181,123 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">561
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">908
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9979
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">065
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">23
 </t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>1144</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -2287,13 +2317,13 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2305,13 +2335,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -2320,18 +2351,13 @@
 </t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>44</t>
@@ -2339,20 +2365,25 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84883
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">9226
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -2370,13 +2401,13 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2387,12 +2418,12 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">886
+          <t>83</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2421,16 +2452,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2442,25 +2473,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">4236
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4819
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2472,81 +2503,82 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n"/>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n"/>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>121</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">9416
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>553</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>40948</t>
+          <t xml:space="preserve">1004
+</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2565,7 +2597,8 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t xml:space="preserve">579
+</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2576,8 +2609,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2586,15 +2618,15 @@
 </t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -2604,41 +2636,30 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>222</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">034
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4381
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n"/>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">237
@@ -2647,30 +2668,29 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>431</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">3130
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>4442</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2680,9 +2700,9 @@
 </t>
         </is>
       </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1909
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -2694,7 +2714,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2718,32 +2738,33 @@
 </t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">143
 </t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">397
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">98
 </t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2755,7 +2776,8 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>03</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="L18" s="3" t="n"/>
@@ -2767,27 +2789,28 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9986
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="R18" s="8" t="inlineStr">
+          <t>124</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
@@ -2795,48 +2818,43 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7420
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="n"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">767
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>6340880</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2852,57 +2870,70 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>14251</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 85 2
+</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+      <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2913,13 +2944,12 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -2931,7 +2961,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -2942,13 +2972,13 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2978,24 +3008,19 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">193
 </t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
+      <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">93
@@ -3004,7 +3029,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3016,24 +3041,24 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -3045,58 +3070,53 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>131</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="n"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3122,10 +3142,11 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
 </t>
@@ -3139,7 +3160,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3151,102 +3172,102 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">809
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -3266,7 +3287,8 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3277,64 +3299,65 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">165
 </t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11888
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
+          <t xml:space="preserve">1060
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
@@ -3349,49 +3372,49 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">892
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">889
-</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
@@ -3422,25 +3445,25 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3464,30 +3487,36 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">066
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3500,14 +3529,13 @@
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3280
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3524,7 +3552,8 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">261
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3535,7 +3564,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>763</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3551,30 +3580,29 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
+      <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3585,15 +3613,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">017
-</t>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3604,24 +3631,23 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="n"/>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
-      </c>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">231
 </t>
         </is>
       </c>
-      <c r="R24" s="8" t="inlineStr">
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
@@ -3629,49 +3655,48 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">3281
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">731
 </t>
         </is>
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>300407</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3689,55 +3714,41 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
+      <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122 1
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">372
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -3748,69 +3759,48 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n"/>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">11561
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="3" t="n"/>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="V25" s="3" t="n"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="n"/>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4158
+41419
+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="n"/>
+      <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -3824,68 +3814,64 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n"/>
+          <t xml:space="preserve">115178685
+1149791
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
+          <t>153</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -3897,60 +3883,62 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">064
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="n"/>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="Q26" s="3" t="n"/>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -3967,128 +3955,133 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">379
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">153
 </t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>043</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">000
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -4105,16 +4098,21 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -4124,15 +4122,10 @@
 </t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
+      <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -4143,38 +4136,37 @@
 </t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
+      <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n"/>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1610
+</t>
+        </is>
+      </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">9360
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="8" t="inlineStr">
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -4182,54 +4174,55 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">411
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4249,129 +4242,135 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="n"/>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>443</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">990
 </t>
         </is>
       </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>4343</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="W29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -4390,14 +4389,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11168
-</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n"/>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -4409,19 +4413,19 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4430,92 +4434,99 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K30" s="3" t="n"/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42138
+          <t xml:space="preserve">667
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>42501</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4533,46 +4544,46 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n"/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+89191911
+</t>
+        </is>
+      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">943
+</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">769
@@ -4581,7 +4592,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -4593,51 +4604,59 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n"/>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">999
+          <t>99921</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">612
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">081
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="n"/>
+          <t xml:space="preserve">892
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">959
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4132
+</t>
+        </is>
+      </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -4649,12 +4668,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">81911955
+111
 </t>
         </is>
       </c>
@@ -4673,7 +4693,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0884
+          <t xml:space="preserve">3646
 </t>
         </is>
       </c>
@@ -4685,7 +4705,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144 1
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
@@ -4697,7 +4717,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4709,20 +4729,20 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -4734,73 +4754,79 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809
+          <t xml:space="preserve">2007
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">781
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">19 1 6
+</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70 6
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 84
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 13
+          <t xml:space="preserve">18 1
 </t>
         </is>
       </c>
@@ -4819,34 +4845,34 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
+          <t xml:space="preserve">4402
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>8133</t>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>1813</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
@@ -4855,92 +4881,97 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>393</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n"/>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">948
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4957,10 +4988,15 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -4970,16 +5006,15 @@
 </t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4987,41 +5022,46 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="n"/>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426
+</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -5030,51 +5070,56 @@
           <t>212</t>
         </is>
       </c>
-      <c r="R34" s="3" t="n"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5091,10 +5136,16 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -5105,30 +5156,30 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -5140,20 +5191,23 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n"/>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">452
+</t>
+        </is>
+      </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
@@ -5163,50 +5217,45 @@
 </t>
         </is>
       </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">769
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">9868
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="X35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5218,7 +5267,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2186
+          <t xml:space="preserve">384
 </t>
         </is>
       </c>
@@ -5238,130 +5287,136 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">079
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">759
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">665
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">664
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2920
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5381,7 +5436,7 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5393,7 +5448,8 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">422112
+214101
 </t>
         </is>
       </c>
@@ -5403,28 +5459,36 @@
 </t>
         </is>
       </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">455266
+72
+45
+61194929
+</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
@@ -5436,13 +5500,13 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9878
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -5454,13 +5518,13 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -5471,15 +5535,22 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t xml:space="preserve">2191
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">816
@@ -5488,17 +5559,18 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">4225
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5515,123 +5587,131 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
           <t>4841</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="n"/>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">676
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1372
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
+          <t xml:space="preserve">4960
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0180
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="n"/>
+          <t xml:space="preserve">728
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792
+</t>
+        </is>
+      </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3809
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">664
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5650,10 +5730,10 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">237
 </t>
@@ -5673,38 +5753,39 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+141
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -5715,53 +5796,53 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
+          <t xml:space="preserve">381
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">661
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -5770,15 +5851,10 @@
 </t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">670
-</t>
-        </is>
-      </c>
+      <c r="Y39" s="3" t="n"/>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5797,7 +5873,8 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
+          <t xml:space="preserve">227
+6443
 </t>
         </is>
       </c>
@@ -5806,15 +5883,15 @@
           <t>259</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">851
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5826,78 +5903,79 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">789
+</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -5909,13 +5987,12 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -5926,7 +6003,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5943,21 +6020,16 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4088
-</t>
-        </is>
-      </c>
+      <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1597
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -5975,7 +6047,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>343</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -5986,75 +6058,71 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">013
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">700
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="n"/>
       <c r="N41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">726
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">470
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
           <t>217</t>
@@ -6066,21 +6134,21 @@
 </t>
         </is>
       </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+      <c r="X41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6099,13 +6167,13 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6094
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -6122,43 +6190,40 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">472
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">56
+</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">013
-</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -6176,25 +6241,15 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="n"/>
+      <c r="S42" s="3" t="n"/>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
@@ -6206,7 +6261,7 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6218,7 +6273,7 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -6229,7 +6284,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
@@ -6248,144 +6303,129 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">60944
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">064
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -6404,7 +6444,8 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
+          <t xml:space="preserve">622
+2722208602828
 </t>
         </is>
       </c>
@@ -6414,27 +6455,22 @@
 </t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">017
-</t>
-        </is>
-      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -6450,39 +6486,33 @@
 </t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+      <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="M44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50020
-</t>
-        </is>
-      </c>
-      <c r="N44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101101101
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6494,56 +6524,34 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="S44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0110
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1501151000115
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n"/>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19898
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24222
+7
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6565,7 +6573,8 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">672727
+</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6575,7 +6584,8 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">84
+24222
 </t>
         </is>
       </c>
@@ -6587,22 +6597,17 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6611,24 +6616,20 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6022
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6219
+          <t xml:space="preserve">61972
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4980
+          <t xml:space="preserve">6242
 </t>
         </is>
       </c>
@@ -6647,49 +6648,50 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">8272
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29298
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
+          <t xml:space="preserve">12089
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3288
+          <t xml:space="preserve">378
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6707,24 +6709,25 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t xml:space="preserve">107
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6740,52 +6743,45 @@
 </t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
-        </is>
-      </c>
-      <c r="P46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
-</t>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6796,49 +6792,39 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
-</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="V46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">831
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">29180
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="3" t="n"/>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
@@ -741,127 +741,129 @@
 </t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="n"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2668
+</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="W4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -879,24 +881,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
-</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2651</t>
+          <t xml:space="preserve">15643
+</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -905,7 +907,7 @@
           <t>425</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">135
 </t>
@@ -913,12 +915,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -928,9 +930,9 @@
 </t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -940,41 +942,39 @@
 </t>
         </is>
       </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-990
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -986,11 +986,10 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
+          <t>203</t>
+        </is>
+      </c>
+      <c r="W5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
@@ -1004,14 +1003,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1029,11 +1027,11 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
-</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+          <t xml:space="preserve">3380
+</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
@@ -1041,8 +1039,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1051,27 +1048,32 @@
 </t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11416
+</t>
+        </is>
+      </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1080,45 +1082,44 @@
           <t>43</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9942
+</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>217</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">6718
 </t>
         </is>
       </c>
@@ -1130,29 +1131,29 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>120</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9310
+          <t xml:space="preserve">1930
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">11039
 </t>
         </is>
       </c>
@@ -1171,7 +1172,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3552
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
@@ -1181,131 +1182,114 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">146
 </t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">771
+          <t>522</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
+          <t xml:space="preserve">2985
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">94
 </t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="n"/>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1324,132 +1308,132 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">3779
+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49712
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">72
 </t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27219
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
+      <c r="V8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="X8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">928
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9178
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">1850
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
@@ -1466,71 +1450,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1825281
+</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1260
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>550</t>
+          <t xml:space="preserve">550
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1543,49 +1526,51 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8929
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">1956
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t xml:space="preserve">9988
+</t>
         </is>
       </c>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">8712
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4290
+          <t xml:space="preserve">194290
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1601,45 +1586,40 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3650
+</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1650,73 +1630,55 @@
 </t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6379
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">430
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="X10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
+      <c r="W10" s="3" t="n"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1728,7 +1690,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
@@ -1747,127 +1709,127 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77871
+          <t xml:space="preserve">3296
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2531
-228548177
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>133</t>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n"/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>2213</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>8114</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2895
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">720
+</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t>4841</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1883,64 +1845,81 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n"/>
+          <t xml:space="preserve">5212
+</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">737
+          <t>145</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277275
-163
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">2999
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1949,21 +1928,21 @@
 </t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">469
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
@@ -1973,7 +1952,7 @@
 </t>
         </is>
       </c>
-      <c r="V12" s="3" t="inlineStr">
+      <c r="V12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">212
 </t>
@@ -1981,24 +1960,25 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850
+          <t xml:space="preserve">2840
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2017,44 +1997,41 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">94556
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2065,34 +2042,39 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>447</t>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7176
+</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -2101,25 +2083,24 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>493</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2131,25 +2112,25 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">078
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2166,8 +2147,13 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203199
+</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
@@ -2175,70 +2161,67 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">561
-</t>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>316</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">8202
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9979
+          <t xml:space="preserve">9290
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2260,44 +2243,34 @@
 </t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">065
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">718
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="n"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
@@ -2314,7 +2287,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4845
+</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">267
@@ -2323,110 +2301,94 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1007
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="inlineStr">
         <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84883
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9226
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+      <c r="X15" s="3" t="n"/>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">848
@@ -2435,7 +2397,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -2454,44 +2416,43 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">23269
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1272
 </t>
         </is>
       </c>
-      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">2957
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4236
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1954819
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2503,82 +2464,89 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="n"/>
+          <t xml:space="preserve">1669
+</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">194910
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t xml:space="preserve">929
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t xml:space="preserve">9290
+</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2594,72 +2562,76 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>4145</t>
+        </is>
+      </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">653
-</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">620
-</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">891
-</t>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1191
+</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8241
+</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4381
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n"/>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">237
@@ -2668,10 +2640,10 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
+          <t>41</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
@@ -2679,42 +2651,42 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>4442</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">5626
+</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+          <t>182</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">8980
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">2974
 </t>
         </is>
       </c>
@@ -2731,14 +2703,19 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3357
+</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">143
 </t>
@@ -2746,7 +2723,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2756,105 +2733,91 @@
 </t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7190
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="n"/>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">767
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>6340880</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2872,68 +2835,74 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 85 2
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
+          <t>224</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11626
 </t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1968
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>143</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2949,22 +2918,18 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
+          <t xml:space="preserve">1561
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="n"/>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">175
 </t>
@@ -2972,13 +2937,13 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">8948
 </t>
         </is>
       </c>
@@ -3001,76 +2966,70 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4949
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12494
+</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -3081,48 +3040,44 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="S20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="n"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>434</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="n"/>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3139,46 +3094,56 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3793
+</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+          <t>138</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1796
+</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -3190,24 +3155,20 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3219,7 +3180,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3229,48 +3190,33 @@
 </t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+      <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
       <c r="V21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3284,87 +3230,81 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5089
+</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
+          <t>458</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1132
+</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">517
+</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
+          <t xml:space="preserve">1970
+</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="n"/>
+      <c r="R22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">187
 </t>
@@ -3372,52 +3312,44 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3433,138 +3365,137 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">20894
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">11285
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">11614
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">294890
+</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">066
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">11136
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="n"/>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1918
+</t>
+        </is>
+      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">23280
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t xml:space="preserve">12198
+</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">1863
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
+          <t xml:space="preserve">94290
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>763</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3582,124 +3513,110 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n"/>
+          <t xml:space="preserve">4379 18
+</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0256
+</t>
+        </is>
+      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215659
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n"/>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">978
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="n"/>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3281
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="V24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
-        </is>
-      </c>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">731
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1894
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="n"/>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t>300407</t>
+          <t xml:space="preserve">88812
+</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3713,94 +3630,132 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2336
+</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122 1
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="inlineStr">
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8726
+</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">372
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="n"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">020
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4158
-41419
-</t>
-        </is>
-      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="n"/>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -3814,128 +3769,136 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2583
+</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115178685
-1149791
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>016</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">064
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>643</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="n"/>
+          <t xml:space="preserve">9318
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -3952,136 +3915,125 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5358
+</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2245
 </t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">379
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0916
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1835
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="n"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="n"/>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4100,129 +4052,126 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1817
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="n"/>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1610
-</t>
-        </is>
-      </c>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9360
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="n"/>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411
+          <t>422</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4239,138 +4188,129 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3091
+</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">9910
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>4241</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8561
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
+      <c r="W29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19910
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4389,54 +4329,55 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15699
+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1168
 </t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">15449
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">16294
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">1769
 </t>
         </is>
       </c>
@@ -4446,87 +4387,70 @@
 </t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>4449244</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">2121
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">667
+          <t xml:space="preserve">94138
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1829
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="n"/>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">9220
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4544,137 +4468,129 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">3140
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-89191911
-</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>624</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">769
-</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
+          <t xml:space="preserve">084
+</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>99921</t>
+          <t xml:space="preserve">859
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
-        </is>
-      </c>
-      <c r="Q31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">024
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4132
+          <t xml:space="preserve">81154
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">063
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">1 85
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>42221</t>
+          <t xml:space="preserve">950
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81911955
-111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4693,143 +4609,105 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3646
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">3642
+</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">579
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28213
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2007
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="n"/>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">781
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19 1 6
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">911
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n"/>
+      <c r="T32" s="3" t="n"/>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70 6
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="n"/>
+      <c r="W32" s="3" t="n"/>
+      <c r="X32" s="3" t="n"/>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18 1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">960
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -4845,133 +4723,126 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4402
+          <t xml:space="preserve">4112
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1817
+</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>393</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10972
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">948
-</t>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01912
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
         </is>
       </c>
       <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
+      <c r="T33" s="3" t="n"/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9800
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -4990,136 +4861,121 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
+          <t>11444</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1452
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2990
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">426
-</t>
-        </is>
-      </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">778
-</t>
-        </is>
-      </c>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="n"/>
+      <c r="T34" s="3" t="n"/>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
+          <t>432</t>
+        </is>
+      </c>
+      <c r="X34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5138,34 +4994,34 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
@@ -5173,101 +5029,100 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">452
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212818
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="n"/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9868
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="n"/>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>484</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">2840
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">384
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5284,25 +5139,30 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6132
+</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>4495</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">113
 </t>
@@ -5310,88 +5170,77 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">079
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">759
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">006
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">665
-</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1616
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="n"/>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="inlineStr">
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
@@ -5399,24 +5248,24 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+          <t>412</t>
+        </is>
+      </c>
+      <c r="X36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5433,145 +5282,142 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>197824</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">11184
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422112
-214101
+          <t xml:space="preserve">10922
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455266
-72
-45
-61194929
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">16815
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">94920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
-</t>
+          <t>3821914</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2332
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">1816
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">880
+</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4225
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5589,129 +5435,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>4841</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">4956
+</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">741
+</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1372
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n"/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">913
+</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4960
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">034
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>4012</t>
-        </is>
-      </c>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">792
-</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
+          <t>302</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="S38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1720
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">664
+</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81014
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="n"/>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">01846
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -5730,128 +5569,121 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">6243
+</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-141
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21202
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">381
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">012
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="S39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">505
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="n"/>
+      <c r="W39" s="3" t="n"/>
+      <c r="X39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1628
+</t>
+        </is>
+      </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">32
@@ -5873,25 +5705,25 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-6443
-</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>259</t>
+          <t xml:space="preserve">6377
+</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -5901,64 +5733,64 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1100
+</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -5969,17 +5801,17 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">0488
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">223
 </t>
@@ -5987,23 +5819,24 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t>161</t>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="X40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -6020,135 +5853,121 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7943
+</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">013
+</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1208
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">019
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n"/>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">179
 </t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 1 4
+</t>
+        </is>
+      </c>
+      <c r="W41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">700
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">726
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">488
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
       <c r="X41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -6173,39 +5992,49 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="n"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4709
+</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1224
+</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">359
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6215,24 +6044,14 @@
 </t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
+      <c r="M42" s="3" t="n"/>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="n"/>
       <c r="P42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">04
@@ -6241,15 +6060,25 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="n"/>
-      <c r="S42" s="3" t="n"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">9490
 </t>
         </is>
       </c>
@@ -6261,11 +6090,11 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -6273,18 +6102,19 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">158
+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6303,82 +6133,74 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60944
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">064
-</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6044
+</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>4340</t>
         </is>
       </c>
       <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
+      <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n"/>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="n"/>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6390,19 +6212,19 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6413,19 +6235,19 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
+          <t xml:space="preserve">7298
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6442,115 +6264,29 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">622
-2722208602828
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
+      <c r="O44" s="3" t="n"/>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
+      <c r="R44" s="3" t="n"/>
       <c r="S44" s="3" t="n"/>
       <c r="T44" s="3" t="n"/>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24222
-7
-</t>
-        </is>
-      </c>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="n"/>
       <c r="W44" s="3" t="n"/>
       <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
+      <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -6573,19 +6309,18 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672727
-</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>534</t>
+          <t xml:space="preserve">036
+</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-24222
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6597,100 +6332,113 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="n"/>
+          <t xml:space="preserve">11819
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6022
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n"/>
+          <t xml:space="preserve">3564
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">559
+</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61972
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6242
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n"/>
+          <t>4960</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">11263
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8272
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">12822
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12089
+          <t xml:space="preserve">11089
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">10609
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">378
+          <t xml:space="preserve">23028 1
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6709,31 +6457,30 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">2239
+</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">925
-</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
+          <t>405</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5034
 </t>
         </is>
       </c>
@@ -6743,91 +6490,83 @@
 </t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">559
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1113
+</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="n"/>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">892
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
+          <t xml:space="preserve">044
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">353
+</t>
+        </is>
+      </c>
+      <c r="R46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="n"/>
+      <c r="T46" s="3" t="n"/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8654
+</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29180
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
@@ -741,7 +741,7 @@
 </t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -749,7 +749,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -759,16 +759,21 @@
 </t>
         </is>
       </c>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -780,7 +785,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -792,13 +797,13 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -808,21 +813,22 @@
 </t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="Q4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2668
-</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>211</t>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">893
+</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -837,15 +843,21 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="3" t="n"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="W4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -857,13 +869,14 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -881,19 +894,20 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15643
-</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+          <t xml:space="preserve">1645
+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">255
 </t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -904,7 +918,8 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -915,22 +930,23 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
 </t>
@@ -950,17 +966,23 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
+          <t xml:space="preserve">958
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="R5" s="8" t="inlineStr">
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -986,12 +1008,13 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="W5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1003,13 +1026,14 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1033,29 +1057,31 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">049
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">101
+</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">11416
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
@@ -1067,30 +1093,31 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9942
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">215621
 </t>
         </is>
       </c>
@@ -1100,7 +1127,12 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -1109,17 +1141,19 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6718
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
@@ -1131,29 +1165,31 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11039
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1172,7 +1208,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
+          <t xml:space="preserve">2552
 </t>
         </is>
       </c>
@@ -1182,7 +1218,7 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">146
 </t>
@@ -1194,25 +1230,27 @@
 </t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">801
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -1224,12 +1262,14 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>522</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1240,11 +1280,16 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2985
-</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="n"/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -1253,10 +1298,16 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">770
@@ -1271,19 +1322,25 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="n"/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1308,7 +1365,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
+          <t xml:space="preserve">3778
 </t>
         </is>
       </c>
@@ -1324,49 +1381,57 @@
 </t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>52</t>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">49712
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -1378,26 +1443,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="S8" s="3" t="n"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -1409,13 +1479,13 @@
       </c>
       <c r="V8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9178
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -1427,13 +1497,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1452,17 +1522,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825281
+          <t xml:space="preserve">18252
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">715
+</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">990
@@ -1471,13 +1546,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">050
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
@@ -1489,38 +1564,49 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">12819
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">749
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n"/>
+          <t xml:space="preserve">4238
+</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1532,20 +1618,25 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">9856
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9988
-</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="n"/>
+          <t xml:space="preserve">09101
+</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">955
 </t>
         </is>
       </c>
@@ -1557,19 +1648,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">9498
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194290
+          <t xml:space="preserve">942908
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -1588,7 +1679,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
+          <t xml:space="preserve">36501
 </t>
         </is>
       </c>
@@ -1600,17 +1691,28 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">412
+</t>
+        </is>
+      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">13
@@ -1619,26 +1721,31 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">580
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1648,10 +1755,15 @@
 </t>
         </is>
       </c>
-      <c r="P10" s="3" t="n"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83 8
+</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1673,9 +1785,23 @@
 </t>
         </is>
       </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -1684,13 +1810,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1719,15 +1845,25 @@
 </t>
         </is>
       </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">853
+</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">101
 </t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">107
 </t>
@@ -1735,61 +1871,67 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">097
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">527
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>8114</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2895
+          <t xml:space="preserve">623
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1801,13 +1943,13 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -1817,19 +1959,24 @@
 </t>
         </is>
       </c>
-      <c r="X11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1845,104 +1992,109 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5212
+          <t xml:space="preserve">5811
 </t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">539
+</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">090
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">139
 </t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2999
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
       <c r="S12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">469
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">141046
 </t>
         </is>
       </c>
@@ -1952,13 +2104,13 @@
 </t>
         </is>
       </c>
-      <c r="V12" s="8" t="inlineStr">
+      <c r="V12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
 </t>
         </is>
       </c>
-      <c r="W12" s="3" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">193
 </t>
@@ -1972,13 +2124,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1997,7 +2149,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94556
+          <t xml:space="preserve">5556
 </t>
         </is>
       </c>
@@ -2007,31 +2159,34 @@
 </t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>116</t>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">871
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -2048,30 +2203,31 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7176
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2083,7 +2239,8 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>493</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2094,31 +2251,26 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="n"/>
       <c r="V13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">078
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -2130,7 +2282,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2149,7 +2301,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203199
+          <t xml:space="preserve">0318
 </t>
         </is>
       </c>
@@ -2161,67 +2313,73 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>4415</t>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">045
+</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">96
+</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>435</t>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8202
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9290
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2243,25 +2401,36 @@
 </t>
         </is>
       </c>
-      <c r="T14" s="3" t="n"/>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">718
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">840
@@ -2270,7 +2439,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2299,64 +2468,82 @@
 </t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1007
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
+          <t xml:space="preserve">120821
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">970
 </t>
         </is>
       </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">016
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
@@ -2373,25 +2560,37 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="n"/>
+          <t xml:space="preserve">96480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="n"/>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">8248
 </t>
         </is>
       </c>
@@ -2416,7 +2615,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23269
+          <t xml:space="preserve">230691
 </t>
         </is>
       </c>
@@ -2428,31 +2627,37 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">643
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2957
+          <t xml:space="preserve">957
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1954819
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n"/>
+          <t xml:space="preserve">589
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1397
+</t>
+        </is>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -2464,36 +2669,37 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>844</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194910
+          <t xml:space="preserve">4818
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">11157
 </t>
         </is>
       </c>
@@ -2517,35 +2723,37 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">558
+</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t xml:space="preserve">11004
+</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9290
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -2564,35 +2772,38 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t xml:space="preserve">48141
+</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>430</t>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">971
 </t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8241
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -2601,34 +2812,45 @@
 </t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">139
 </t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">132
 </t>
         </is>
       </c>
-      <c r="N17" s="3" t="n"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2640,7 +2862,8 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
@@ -2651,42 +2874,43 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5626
-</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+          <t xml:space="preserve">626
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">014
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2974
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -2705,13 +2929,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">9557
+</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">009
 </t>
         </is>
       </c>
@@ -2729,48 +2953,73 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
+          <t xml:space="preserve">960
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="n"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="n"/>
+          <t xml:space="preserve">1822
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n"/>
+          <t xml:space="preserve">9809
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2782,23 +3031,23 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="W18" s="8" t="inlineStr">
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">167
 </t>
@@ -2806,18 +3055,20 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">680
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2835,30 +3086,31 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">11626
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1993
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2868,29 +3120,40 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">642
+</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -2902,7 +3165,8 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2911,39 +3175,45 @@
 </t>
         </is>
       </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>134</t>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">794
+</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="n"/>
+          <t xml:space="preserve">361
+</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1995
 </t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -2968,24 +3238,29 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4949
-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n"/>
+          <t xml:space="preserve">14949
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">022
+</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">12494
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
+          <t xml:space="preserve">1958
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
@@ -2993,31 +3268,38 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n"/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t xml:space="preserve">022
+</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="N20" s="3" t="n"/>
@@ -3029,13 +3311,14 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>2214</t>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">035
+</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -3050,34 +3333,45 @@
 </t>
         </is>
       </c>
-      <c r="T20" s="3" t="n"/>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880
+</t>
+        </is>
+      </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="W20" s="3" t="inlineStr">
-        <is>
-          <t>434</t>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="3" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3096,48 +3390,49 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>138</t>
+          <t xml:space="preserve">3713
+</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">036
+</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">916080
+</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1796
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">895
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -3153,22 +3448,27 @@
 </t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n"/>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887
+</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">18080
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3186,18 +3486,23 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">947
-</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
@@ -3205,7 +3510,7 @@
       </c>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -3215,7 +3520,12 @@
 </t>
         </is>
       </c>
-      <c r="Y21" s="3" t="n"/>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
       <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -3236,30 +3546,31 @@
 </t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>458</t>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
@@ -3278,55 +3589,67 @@
 </t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n"/>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">016
 </t>
         </is>
       </c>
-      <c r="Q22" s="3" t="n"/>
-      <c r="R22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">046
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18 7
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -3340,7 +3663,8 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3349,7 +3673,12 @@
 </t>
         </is>
       </c>
-      <c r="Z22" s="3" t="n"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3377,18 +3706,19 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">975
+</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11614
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3400,13 +3730,13 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -3418,83 +3748,91 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">2071
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294890
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11136
+          <t xml:space="preserve">115136
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t xml:space="preserve">915
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23280
+          <t xml:space="preserve">3280
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12198
+          <t xml:space="preserve">1498
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">9389
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
+          <t xml:space="preserve">4298
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">11963
 </t>
         </is>
       </c>
@@ -3513,30 +3851,40 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4379 18
+          <t xml:space="preserve">49729
 </t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0256
-</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">215659
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="n"/>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">085
+</t>
+        </is>
+      </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">22
@@ -3545,14 +3893,20 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t xml:space="preserve">597
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 4
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
@@ -3561,7 +3915,12 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="3" t="n"/>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">978
@@ -3570,24 +3929,31 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="Q24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
-</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="n"/>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">853
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -3599,14 +3965,19 @@
       </c>
       <c r="V24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="n"/>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88812
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">731
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -3616,7 +3987,12 @@
 </t>
         </is>
       </c>
-      <c r="Z24" s="3" t="n"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3632,89 +4008,95 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
+          <t xml:space="preserve">2536
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8726
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1539
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">21356
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">020
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
+          <t xml:space="preserve">962
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="R25" s="8" t="inlineStr">
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
 </t>
@@ -3728,31 +4110,43 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>1114</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n"/>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">719
+</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3771,7 +4165,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2583
+          <t xml:space="preserve">2683
 </t>
         </is>
       </c>
@@ -3781,7 +4175,7 @@
 </t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">153
 </t>
@@ -3789,13 +4183,13 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3813,12 +4207,17 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="8" t="inlineStr">
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
@@ -3826,23 +4225,29 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n"/>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">010
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
+          <t xml:space="preserve">888080
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -3850,7 +4255,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -3862,13 +4267,13 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9318
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3880,25 +4285,25 @@
       </c>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -3917,73 +4322,89 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5358
-</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2245
-</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
+          <t xml:space="preserve">93517
+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">133
 </t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13125
 </t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0916
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n"/>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1835
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n"/>
+          <t xml:space="preserve">735
+</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
+          <t xml:space="preserve">0
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -3991,7 +4412,8 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -4012,9 +4434,9 @@
 </t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -4024,10 +4446,15 @@
 </t>
         </is>
       </c>
-      <c r="X27" s="3" t="n"/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -4052,7 +4479,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
@@ -4068,9 +4495,9 @@
 </t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1817
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -4080,19 +4507,25 @@
 </t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="I28" s="3" t="n"/>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">075
+</t>
+        </is>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">328
 </t>
@@ -4100,32 +4533,44 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n"/>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
 </t>
         </is>
       </c>
-      <c r="P28" s="3" t="n"/>
-      <c r="Q28" s="8" t="inlineStr">
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
         </is>
       </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>422</t>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -4136,13 +4581,13 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4152,9 +4597,10 @@
 </t>
         </is>
       </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t>412</t>
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
@@ -4202,79 +4648,96 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0185
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9910
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="n"/>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8561
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
@@ -4284,33 +4747,33 @@
 </t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">858
-</t>
-        </is>
-      </c>
-      <c r="W29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19910
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4347,19 +4810,19 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15449
+          <t xml:space="preserve">6499
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16294
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -4371,38 +4834,49 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
+          <t xml:space="preserve">749
+</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">745
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>4449244</t>
+          <t xml:space="preserve">4910
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121
+          <t xml:space="preserve">4121
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">9989
 </t>
         </is>
       </c>
@@ -4414,43 +4888,50 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94138
+          <t xml:space="preserve">41351
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">857
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="n"/>
+          <t xml:space="preserve">8294
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220
+          <t xml:space="preserve">65480
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4472,9 +4953,9 @@
 </t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -4492,11 +4973,11 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+          <t xml:space="preserve">904
+</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">125
 </t>
@@ -4504,35 +4985,44 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="n"/>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">14544
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -4541,47 +5031,42 @@
 </t>
         </is>
       </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">078
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81154
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">063
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 85
-</t>
-        </is>
-      </c>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80101
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="n"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">950
@@ -4590,7 +5075,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -4613,68 +5098,75 @@
 </t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">579
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>4111</t>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319
+</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">28213
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n"/>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>793</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">751
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="n"/>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -4690,24 +5182,54 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" s="3" t="n"/>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="3" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1817
+</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+          <t xml:space="preserve">1960
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -4735,7 +5257,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -4747,48 +5269,55 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n"/>
+          <t xml:space="preserve">10080
+</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10972
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">049
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4798,51 +5327,63 @@
 </t>
         </is>
       </c>
-      <c r="Q33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01912
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="n"/>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">916
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">864
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">718
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="X33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4861,18 +5402,19 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t xml:space="preserve">2114
+</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1972
+</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1597
 </t>
         </is>
       </c>
@@ -4884,98 +5426,121 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">003
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">985
+</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n"/>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">969
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" s="3" t="n"/>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="X34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5000,7 +5565,8 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -5011,7 +5577,7 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1818
 </t>
         </is>
       </c>
@@ -5029,12 +5595,13 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -5050,15 +5617,15 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212818
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5076,22 +5643,28 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
@@ -5100,29 +5673,31 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5147,42 +5722,43 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>4495</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">7138
+</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0995
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">1059
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5194,49 +5770,61 @@
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1616
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="n"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5248,24 +5836,25 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="X36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5284,7 +5873,8 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>197824</t>
+          <t xml:space="preserve">20782
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5295,30 +5885,31 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10922
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">8194
 </t>
         </is>
       </c>
@@ -5330,76 +5921,79 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
+          <t xml:space="preserve">50717
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16815
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94920
+          <t xml:space="preserve">4920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t xml:space="preserve">1010
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>3821914</t>
+          <t xml:space="preserve">3809
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2332
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t xml:space="preserve">900
+</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
@@ -5411,13 +6005,14 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">4299
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5439,81 +6034,98 @@
 </t>
         </is>
       </c>
-      <c r="D38" s="3" t="n"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">849
+</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0251
 </t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">913
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>135</t>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>182</t>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1170
+</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -5523,34 +6135,39 @@
 </t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">664
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">81014
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="n"/>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01846
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -5569,7 +6186,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
+          <t xml:space="preserve">6641
 </t>
         </is>
       </c>
@@ -5579,15 +6196,15 @@
 </t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">119
 </t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1815
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5599,32 +6216,43 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="n"/>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21202
+          <t xml:space="preserve">8 1
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5634,7 +6262,7 @@
 </t>
         </is>
       </c>
-      <c r="P39" s="8" t="inlineStr">
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">012
 </t>
@@ -5642,51 +6270,61 @@
       </c>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
+          <t xml:space="preserve">5210
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
+          <t xml:space="preserve">1960
+</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
         </is>
       </c>
-      <c r="V39" s="3" t="n"/>
-      <c r="W39" s="3" t="n"/>
-      <c r="X39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">988
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="W39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">625
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5709,7 +6347,7 @@
 </t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -5717,7 +6355,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5729,7 +6367,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -5748,25 +6386,25 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -5778,30 +6416,31 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0488
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
@@ -5811,18 +6450,19 @@
 </t>
         </is>
       </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="X40" s="8" t="inlineStr">
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
@@ -5830,13 +6470,13 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -5855,7 +6495,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7943
+          <t xml:space="preserve">6943
 </t>
         </is>
       </c>
@@ -5865,109 +6505,135 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">726
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 37
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">013
-</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1208
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="n"/>
-      <c r="P41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">019
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="n"/>
+          <t xml:space="preserve">053
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2935
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">581
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">470
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 1 4
-</t>
-        </is>
-      </c>
-      <c r="W41" s="8" t="inlineStr">
+          <t xml:space="preserve">813
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="X41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -5986,7 +6652,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
@@ -5998,37 +6664,37 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4709
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">1817
+</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">538
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">359
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6038,20 +6704,30 @@
 </t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n"/>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">04
@@ -6060,7 +6736,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -6072,19 +6748,19 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">474
 </t>
         </is>
       </c>
@@ -6094,7 +6770,7 @@
 </t>
         </is>
       </c>
-      <c r="W42" s="8" t="inlineStr">
+      <c r="W42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -6102,19 +6778,19 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -6133,17 +6809,17 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
-</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
+          <t xml:space="preserve">6094
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">261
 </t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
@@ -6152,46 +6828,64 @@
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">16 279
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>4340</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10219
+</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n"/>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
@@ -6212,42 +6906,43 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">680
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">399
 </t>
         </is>
       </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7298
-</t>
-        </is>
-      </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2119
 </t>
         </is>
       </c>
@@ -6264,7 +6959,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -6309,18 +7009,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t xml:space="preserve">1319
+</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">036
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -6338,7 +7039,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11819
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
@@ -6350,13 +7051,13 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">0800
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3564
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
@@ -6368,77 +7069,79 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t xml:space="preserve">4900
+</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12822
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>798</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11089
+          <t xml:space="preserve">1089
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10609
+          <t xml:space="preserve">6580
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028 1
+          <t xml:space="preserve">3828
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">2815
 </t>
         </is>
       </c>
@@ -6461,76 +7164,87 @@
 </t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">262
 </t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>405</t>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1015
+</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5034
+          <t xml:space="preserve">2004
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11110
+</t>
+        </is>
+      </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">12198
 </t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">351
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9001
+</t>
+        </is>
+      </c>
+      <c r="P46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6540,8 +7254,18 @@
 </t>
         </is>
       </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n"/>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598
+</t>
+        </is>
+      </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8654
@@ -6550,24 +7274,29 @@
       </c>
       <c r="V46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15416
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -797,7 +797,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -809,13 +809,13 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -825,9 +825,9 @@
 </t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">893
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -839,7 +839,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -855,9 +855,9 @@
 </t>
         </is>
       </c>
-      <c r="W4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -894,7 +894,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">146495
 </t>
         </is>
       </c>
@@ -904,7 +904,7 @@
 </t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
 </t>
@@ -912,7 +912,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -942,7 +942,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -966,7 +966,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1008,11 +1008,11 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="W5" s="8" t="inlineStr">
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">179
 </t>
@@ -1032,8 +1032,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1055,19 +1054,19 @@
 </t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">049
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">197
 </t>
@@ -1079,9 +1078,9 @@
 </t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1099,25 +1098,25 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">215621
+          <t xml:space="preserve">2561
 </t>
         </is>
       </c>
@@ -1127,12 +1126,7 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+      <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -1177,7 +1171,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -1189,7 +1183,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1208,7 +1202,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552
+          <t xml:space="preserve">3537
 </t>
         </is>
       </c>
@@ -1224,7 +1218,7 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
@@ -1262,7 +1256,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -1280,7 +1274,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1304,19 +1298,19 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1365,7 +1359,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3778
+          <t xml:space="preserve">3779
 </t>
         </is>
       </c>
@@ -1375,15 +1369,15 @@
 </t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1405,9 +1399,9 @@
 </t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1417,7 +1411,7 @@
 </t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">152
 </t>
@@ -1425,25 +1419,25 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1477,15 +1471,15 @@
 </t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1534,7 +1528,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">713
 </t>
         </is>
       </c>
@@ -1546,7 +1540,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -1562,15 +1556,10 @@
 </t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12819
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -1582,31 +1571,31 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4238
+          <t xml:space="preserve">4220
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1033
 </t>
         </is>
       </c>
@@ -1618,13 +1607,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9856
+          <t xml:space="preserve">92856
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09101
+          <t xml:space="preserve">8911
 </t>
         </is>
       </c>
@@ -1648,19 +1637,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9498
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942908
+          <t xml:space="preserve">94298
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -1691,7 +1680,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -1703,13 +1692,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -1721,31 +1710,31 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1757,7 +1746,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83 8
+          <t xml:space="preserve">6 2
 </t>
         </is>
       </c>
@@ -1781,22 +1770,23 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">191
 </t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="W10" s="8" t="inlineStr">
+      <c r="W10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
@@ -1841,19 +1831,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
-</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">333
+</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -1883,25 +1873,25 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">2 316
 </t>
         </is>
       </c>
@@ -1913,13 +1903,13 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">623
+          <t xml:space="preserve">023
 </t>
         </is>
       </c>
@@ -1929,9 +1919,9 @@
 </t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -1943,31 +1933,31 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="W11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -1992,7 +1982,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5811
+          <t xml:space="preserve">5011
 </t>
         </is>
       </c>
@@ -2002,9 +1992,9 @@
 </t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">539
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -2016,13 +2006,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
@@ -2032,12 +2022,7 @@
 </t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -2046,7 +2031,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2058,19 +2043,19 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2080,13 +2065,13 @@
 </t>
         </is>
       </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">129
 </t>
@@ -2094,7 +2079,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141046
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -2130,7 +2115,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2149,7 +2134,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5556
+          <t xml:space="preserve">1556
 </t>
         </is>
       </c>
@@ -2159,21 +2144,21 @@
 </t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -2201,21 +2186,21 @@
 </t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -2227,7 +2212,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2243,9 +2228,9 @@
 </t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -2255,16 +2240,21 @@
 </t>
         </is>
       </c>
-      <c r="U13" s="3" t="n"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2282,7 +2272,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2301,11 +2291,11 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0318
-</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+          <t xml:space="preserve">0329
+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
@@ -2325,7 +2315,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">045
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2343,13 +2333,13 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2365,9 +2355,9 @@
 </t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">843
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
@@ -2403,13 +2393,13 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
+          <t xml:space="preserve">1711
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2419,15 +2409,15 @@
 </t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -2458,7 +2448,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
+          <t xml:space="preserve">4545
 </t>
         </is>
       </c>
@@ -2468,7 +2458,7 @@
 </t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">149
 </t>
@@ -2486,15 +2476,15 @@
 </t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120821
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2512,19 +2502,19 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2540,7 +2530,7 @@
 </t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">257
 </t>
@@ -2560,11 +2550,11 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
+          <t xml:space="preserve">2480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
 </t>
@@ -2578,19 +2568,19 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -2615,7 +2605,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230691
+          <t xml:space="preserve">23069
 </t>
         </is>
       </c>
@@ -2627,7 +2617,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">643
+          <t xml:space="preserve">6553
 </t>
         </is>
       </c>
@@ -2645,37 +2635,37 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">589
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1349
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">669
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2687,19 +2677,19 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4818
+          <t xml:space="preserve">4930
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11157
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2729,7 +2719,7 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11004
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
@@ -2741,13 +2731,13 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
+          <t xml:space="preserve">94210
 </t>
         </is>
       </c>
@@ -2772,13 +2762,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48141
-</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">08141
+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -2788,15 +2778,15 @@
 </t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">971
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -2812,21 +2802,20 @@
 </t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -2838,13 +2827,13 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2866,7 +2855,7 @@
 </t>
         </is>
       </c>
-      <c r="S17" s="8" t="inlineStr">
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
@@ -2910,7 +2899,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2933,9 +2922,9 @@
 </t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">009
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2953,31 +2942,26 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
+      <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2989,31 +2973,31 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9809
+          <t xml:space="preserve">9828
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">2168
 </t>
         </is>
       </c>
@@ -3031,31 +3015,31 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="V18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16 7
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -3067,7 +3051,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3086,7 +3070,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
@@ -3098,13 +3082,13 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">630
 </t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1993
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3128,7 +3112,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3138,22 +3122,27 @@
 </t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">642
-</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n"/>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -3165,7 +3154,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -3175,9 +3164,9 @@
 </t>
         </is>
       </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">794
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3189,25 +3178,25 @@
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1995
-</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">985
-</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
@@ -3238,25 +3227,25 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14949
+          <t xml:space="preserve">14979
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
-</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1958
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -3274,29 +3263,29 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
-</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="M20" s="8" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
@@ -3311,13 +3300,13 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">035
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -3327,7 +3316,7 @@
 </t>
         </is>
       </c>
-      <c r="S20" s="8" t="inlineStr">
+      <c r="S20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">167
 </t>
@@ -3335,7 +3324,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3347,13 +3336,13 @@
       </c>
       <c r="V20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3365,7 +3354,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -3394,15 +3383,15 @@
 </t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">036
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">916080
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -3414,19 +3403,19 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3462,7 +3451,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18080
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -3486,7 +3475,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3498,7 +3487,7 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -3508,7 +3497,7 @@
 </t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
+      <c r="W21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
@@ -3516,13 +3505,13 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3546,7 +3535,7 @@
 </t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -3554,20 +3543,19 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3582,7 +3570,12 @@
 </t>
         </is>
       </c>
-      <c r="J22" s="3" t="n"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">517
@@ -3591,19 +3584,19 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1209
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3615,19 +3608,19 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">2246
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 7
+          <t xml:space="preserve">18 54
 </t>
         </is>
       </c>
@@ -3639,13 +3632,13 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3663,7 +3656,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -3700,7 +3693,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11285
+          <t xml:space="preserve">11284
 </t>
         </is>
       </c>
@@ -3718,7 +3711,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
@@ -3748,19 +3741,19 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2071
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
@@ -3770,39 +3763,28 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115136
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9185
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3280
-</t>
+          <t>32606</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
+          <t xml:space="preserve">0498
 </t>
         </is>
       </c>
@@ -3814,13 +3796,13 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9389
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -3832,7 +3814,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11963
+          <t xml:space="preserve">1983
 </t>
         </is>
       </c>
@@ -3851,13 +3833,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49729
+          <t xml:space="preserve">49129
 </t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -3879,9 +3861,9 @@
 </t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">085
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -3893,19 +3875,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">597
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">371
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3915,9 +3892,9 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3927,21 +3904,21 @@
 </t>
         </is>
       </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">919
-</t>
-        </is>
-      </c>
-      <c r="R24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">853
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">944
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3953,7 +3930,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -3969,9 +3946,9 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">731
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3989,7 +3966,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4008,19 +3985,19 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2536
+          <t xml:space="preserve">2236
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1539
+          <t xml:space="preserve">23 1
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4032,19 +4009,18 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">21356
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4056,13 +4032,13 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -4072,51 +4048,51 @@
 </t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -4126,9 +4102,9 @@
 </t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -4140,13 +4116,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">9208
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4181,7 +4157,7 @@
 </t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -4189,34 +4165,29 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">177
 </t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -4225,7 +4196,7 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4237,17 +4208,17 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888080
+          <t xml:space="preserve">9088
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="8" t="inlineStr">
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -4267,7 +4238,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -4285,19 +4256,19 @@
       </c>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="X26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
@@ -4322,7 +4293,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93517
+          <t xml:space="preserve">4358
 </t>
         </is>
       </c>
@@ -4346,19 +4317,19 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">13125
-</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
+          <t xml:space="preserve">1312
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4376,19 +4347,19 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
-</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
@@ -4400,11 +4371,11 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -4422,12 +4393,7 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
+      <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -4436,7 +4402,7 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4454,7 +4420,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -4479,7 +4445,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
@@ -4497,25 +4463,25 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">075
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -4539,7 +4505,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -4581,13 +4547,13 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4642,28 +4608,23 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0185
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">122
@@ -4690,7 +4651,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>37</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
@@ -4719,7 +4680,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -4755,13 +4716,13 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">794
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4773,7 +4734,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4816,7 +4777,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6499
+          <t xml:space="preserve">6459
 </t>
         </is>
       </c>
@@ -4834,7 +4795,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -4846,37 +4807,32 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4910
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4918
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9989
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
@@ -4888,13 +4844,13 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41351
+          <t xml:space="preserve">4131
 </t>
         </is>
       </c>
@@ -4906,31 +4862,31 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8294
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65480
+          <t xml:space="preserve">942280
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -4959,9 +4915,9 @@
 </t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -4977,27 +4933,27 @@
 </t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">125
 </t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">081
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5016,24 +4972,20 @@
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14544
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16441
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
         </is>
       </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">078
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -5045,24 +4997,25 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">92116
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="V31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">80101
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -5075,7 +5028,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5100,13 +5053,13 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -5124,7 +5077,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
@@ -5136,13 +5089,13 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>291</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
@@ -5153,17 +5106,22 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">751
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n"/>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">82
@@ -5178,16 +5136,16 @@
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">80
@@ -5196,13 +5154,13 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="V32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -5212,21 +5170,21 @@
 </t>
         </is>
       </c>
-      <c r="X32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1817
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5257,7 +5215,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -5267,9 +5225,9 @@
 </t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10080
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5297,21 +5255,21 @@
 </t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">049
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">601
 </t>
         </is>
       </c>
@@ -5329,35 +5287,35 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">864
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
@@ -5369,21 +5327,21 @@
 </t>
         </is>
       </c>
-      <c r="X33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5408,13 +5366,13 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1972
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1597
+          <t xml:space="preserve">5719
 </t>
         </is>
       </c>
@@ -5426,7 +5384,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -5444,37 +5402,32 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">003
+          <t xml:space="preserve">023
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n"/>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5484,9 +5437,9 @@
 </t>
         </is>
       </c>
-      <c r="Q34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">969
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -5504,7 +5457,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -5514,7 +5467,7 @@
 </t>
         </is>
       </c>
-      <c r="V34" s="3" t="inlineStr">
+      <c r="V34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
@@ -5526,15 +5479,15 @@
 </t>
         </is>
       </c>
-      <c r="X34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">866
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -5559,13 +5512,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -5577,11 +5530,11 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
-</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">121
 </t>
@@ -5601,7 +5554,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -5623,12 +5576,7 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
+      <c r="N35" s="3" t="n"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -5637,46 +5585,46 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="S35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">688
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">165
@@ -5685,7 +5633,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5722,19 +5670,19 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7138
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0995
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -5746,13 +5694,13 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1059
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -5770,7 +5718,7 @@
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -5782,25 +5730,25 @@
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8708
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5818,17 +5766,17 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
@@ -5842,13 +5790,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5909,7 +5857,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8194
+          <t xml:space="preserve">1814
 </t>
         </is>
       </c>
@@ -5921,7 +5869,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50717
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
@@ -5933,13 +5881,13 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5951,7 +5899,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5969,19 +5917,19 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
+          <t xml:space="preserve">38019
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -6005,13 +5953,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4299
+          <t xml:space="preserve">4222
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6030,14 +5978,13 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4956
-</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
+          <t xml:space="preserve">4156
+</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>837</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -6046,86 +5993,86 @@
 </t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">849
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0251
+          <t xml:space="preserve">0351
 </t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">1702
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02 4
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">904
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -6137,13 +6084,13 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1 6 1
 </t>
         </is>
       </c>
       <c r="V38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6161,13 +6108,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6186,7 +6133,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6641
+          <t xml:space="preserve">6244
 </t>
         </is>
       </c>
@@ -6198,7 +6145,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -6234,13 +6181,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 1
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6252,14 +6198,13 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6268,9 +6213,9 @@
 </t>
         </is>
       </c>
-      <c r="Q39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">698
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -6280,27 +6225,27 @@
 </t>
         </is>
       </c>
-      <c r="S39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5210
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -6312,13 +6257,13 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -6371,7 +6316,11 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="3" t="n"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">38
@@ -6390,7 +6339,7 @@
 </t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">100
 </t>
@@ -6398,7 +6347,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6416,13 +6365,13 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -6434,7 +6383,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -6452,7 +6401,7 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6476,7 +6425,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6495,25 +6444,25 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6943
-</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
+          <t xml:space="preserve">6993
+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">262
 </t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">726
-</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -6523,12 +6472,7 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 37
-</t>
-        </is>
-      </c>
+      <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">47
@@ -6537,7 +6481,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6549,19 +6493,19 @@
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">053
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6577,43 +6521,43 @@
 </t>
         </is>
       </c>
-      <c r="Q41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2935
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">581
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">813
-</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6417
+</t>
+        </is>
+      </c>
+      <c r="W41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
@@ -6621,19 +6565,19 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6652,7 +6596,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
@@ -6662,7 +6606,7 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">104
 </t>
@@ -6676,25 +6620,25 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6704,27 +6648,27 @@
 </t>
         </is>
       </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6734,9 +6678,9 @@
 </t>
         </is>
       </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
+      <c r="Q42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">617
 </t>
         </is>
       </c>
@@ -6758,9 +6702,9 @@
 </t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">474
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -6778,19 +6722,19 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6809,7 +6753,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6094
+          <t xml:space="preserve">50494
 </t>
         </is>
       </c>
@@ -6828,7 +6772,7 @@
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 279
+          <t xml:space="preserve">1 279
 </t>
         </is>
       </c>
@@ -6864,25 +6808,25 @@
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10219
-</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">1227
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9720
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6906,13 +6850,13 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6922,27 +6866,27 @@
 </t>
         </is>
       </c>
-      <c r="W43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">680
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
@@ -7015,13 +6959,13 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -7045,19 +6989,19 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
@@ -7075,13 +7019,13 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -7099,20 +7043,19 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">21725
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -7123,25 +7066,25 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">837
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3828
+          <t xml:space="preserve">3028
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2815
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -7172,25 +7115,25 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004
+          <t xml:space="preserve">10154
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -7206,33 +7149,33 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11110
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">12198
+          <t xml:space="preserve">12138
 </t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">351
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9001
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -7250,7 +7193,7 @@
       </c>
       <c r="R46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -7268,13 +7211,13 @@
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8654
+          <t xml:space="preserve">3654
 </t>
         </is>
       </c>
       <c r="V46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">15416
+          <t xml:space="preserve">18416
 </t>
         </is>
       </c>
@@ -7287,13 +7230,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
@@ -753,7 +753,7 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
@@ -767,16 +767,16 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">110
 </t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">12
@@ -803,7 +803,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -815,11 +815,11 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="8" t="inlineStr">
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">197
 </t>
@@ -839,7 +839,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -849,7 +849,7 @@
 </t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -894,13 +894,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146495
+          <t xml:space="preserve">4645
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -966,13 +966,13 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -982,7 +982,7 @@
 </t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="R5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -990,7 +990,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -1012,9 +1012,9 @@
 </t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
+      <c r="W5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1026,13 +1026,14 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1056,29 +1057,29 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
@@ -1086,7 +1087,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1104,19 +1105,19 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2561
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">942
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -1141,7 +1142,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1171,19 +1172,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3537
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
@@ -1274,7 +1275,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1292,7 +1293,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1304,7 +1305,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -1314,7 +1315,7 @@
 </t>
         </is>
       </c>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -1328,7 +1329,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -1340,7 +1341,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -1383,7 +1384,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
@@ -1425,13 +1426,13 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1461,7 +1462,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1516,7 +1517,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18252
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
@@ -1528,8 +1529,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">713
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1556,7 +1556,12 @@
 </t>
         </is>
       </c>
-      <c r="J9" s="3" t="n"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">289
@@ -1571,25 +1576,25 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1607,13 +1612,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92856
+          <t xml:space="preserve">1986
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8911
+          <t xml:space="preserve">8918
 </t>
         </is>
       </c>
@@ -1625,13 +1630,13 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8712
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
@@ -1643,13 +1648,13 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94298
+          <t xml:space="preserve">94290
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36501
+          <t xml:space="preserve">3650
 </t>
         </is>
       </c>
@@ -1692,7 +1697,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1716,25 +1721,25 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -1746,13 +1751,13 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 2
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -1770,19 +1775,19 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1914
 </t>
         </is>
       </c>
@@ -1825,25 +1830,25 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
+          <t xml:space="preserve">3246
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333
-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">753
+</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">553
 </t>
         </is>
       </c>
@@ -1867,103 +1872,103 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">097
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">023
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12204
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 316
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">023
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
       <c r="V11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">1586
 </t>
         </is>
       </c>
       <c r="W11" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="X11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -1982,13 +1987,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5011
-</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">5111
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -1998,7 +2003,7 @@
 </t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -2010,19 +2015,24 @@
 </t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -2031,55 +2041,55 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2109,13 +2119,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2810
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2134,7 +2144,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
@@ -2144,9 +2154,9 @@
 </t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2158,7 +2168,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2182,17 +2192,17 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
@@ -2200,7 +2210,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2212,7 +2222,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">982
 </t>
         </is>
       </c>
@@ -2224,19 +2234,18 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="S13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
+          <t>93</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">18668
 </t>
         </is>
       </c>
@@ -2266,7 +2275,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
@@ -2291,7 +2300,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0329
+          <t xml:space="preserve">3319
 </t>
         </is>
       </c>
@@ -2309,11 +2318,11 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">145
 </t>
@@ -2343,7 +2352,7 @@
 </t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">125
 </t>
@@ -2351,13 +2360,13 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2369,7 +2378,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2393,13 +2402,13 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">711
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -2411,19 +2420,19 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2448,7 +2457,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4545
+          <t xml:space="preserve">4845
 </t>
         </is>
       </c>
@@ -2472,7 +2481,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -2484,19 +2493,19 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2514,13 +2523,13 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -2550,7 +2559,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
@@ -2574,7 +2583,7 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2586,7 +2595,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -2617,7 +2626,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6553
+          <t xml:space="preserve">652
 </t>
         </is>
       </c>
@@ -2629,7 +2638,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
@@ -2647,13 +2656,13 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1349
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2665,31 +2674,25 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4930
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4320
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
@@ -2713,31 +2716,31 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">2558
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94210
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
@@ -2762,23 +2765,23 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08141
+          <t xml:space="preserve">4614
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">191
 </t>
@@ -2786,7 +2789,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -2804,18 +2807,19 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -2833,7 +2837,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -2851,7 +2855,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2867,15 +2871,15 @@
 </t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">412
+</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
@@ -2899,7 +2903,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -2918,13 +2922,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9557
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">3557
+</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -2946,16 +2950,21 @@
 </t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="I18" s="3" t="n"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2971,21 +2980,21 @@
 </t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9828
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -2997,7 +3006,7 @@
       </c>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2168
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -3015,25 +3024,25 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 7
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -3082,7 +3091,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -3094,11 +3103,11 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
@@ -3112,13 +3121,13 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
@@ -3128,22 +3137,21 @@
 </t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -3154,7 +3162,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -3164,9 +3172,9 @@
 </t>
         </is>
       </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
@@ -3176,15 +3184,15 @@
 </t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -3194,9 +3202,9 @@
 </t>
         </is>
       </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">889
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3227,7 +3235,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14979
+          <t xml:space="preserve">14179
 </t>
         </is>
       </c>
@@ -3237,9 +3245,9 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
@@ -3291,11 +3299,15 @@
 </t>
         </is>
       </c>
-      <c r="N20" s="3" t="n"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -3304,9 +3316,9 @@
 </t>
         </is>
       </c>
-      <c r="Q20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -3324,23 +3336,23 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="W20" s="8" t="inlineStr">
+          <t xml:space="preserve">8 0
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">177
 </t>
@@ -3348,19 +3360,19 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3379,7 +3391,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">3793
 </t>
         </is>
       </c>
@@ -3391,7 +3403,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3401,9 +3413,9 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3415,7 +3427,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3425,9 +3437,9 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">411
 </t>
         </is>
       </c>
@@ -3437,15 +3449,15 @@
 </t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">887
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3469,7 +3481,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3487,7 +3499,7 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -3497,25 +3509,30 @@
 </t>
         </is>
       </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+          <t xml:space="preserve">9181
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3543,19 +3560,20 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3588,9 +3606,9 @@
 </t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1209
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3602,43 +3620,43 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">2970
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2246
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 54
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -3656,7 +3674,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -3693,7 +3711,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11284
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
@@ -3711,7 +3729,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
@@ -3723,8 +3741,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>013</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3735,13 +3752,13 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">807
 </t>
         </is>
       </c>
@@ -3753,8 +3770,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -3763,7 +3779,12 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="3" t="n"/>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1156
@@ -3772,19 +3793,20 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9185
+          <t xml:space="preserve">1915
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t xml:space="preserve">2328
+</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0498
+          <t xml:space="preserve">1498
 </t>
         </is>
       </c>
@@ -3802,7 +3824,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -3814,7 +3836,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -3833,13 +3855,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49129
+          <t xml:space="preserve">4179
 </t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -3849,7 +3871,7 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">195
 </t>
@@ -3857,13 +3879,13 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -3875,14 +3897,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -3894,7 +3916,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3904,9 +3926,9 @@
 </t>
         </is>
       </c>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">944
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3930,7 +3952,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -3942,7 +3964,7 @@
       </c>
       <c r="V24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3954,7 +3976,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -3966,7 +3988,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3985,19 +4007,19 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">2336
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 1
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -4009,7 +4031,8 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">76
+</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -4020,7 +4043,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -4032,25 +4055,25 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4062,13 +4085,13 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -4092,37 +4115,36 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4141,7 +4163,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2683
+          <t xml:space="preserve">2283
 </t>
         </is>
       </c>
@@ -4165,13 +4187,13 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4181,7 +4203,12 @@
 </t>
         </is>
       </c>
-      <c r="J26" s="3" t="n"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">177
@@ -4202,19 +4229,19 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -4226,11 +4253,11 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">191
 </t>
@@ -4238,7 +4265,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4254,30 +4281,20 @@
 </t>
         </is>
       </c>
-      <c r="W26" s="8" t="inlineStr">
+      <c r="W26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">153
 </t>
         </is>
       </c>
-      <c r="X26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
+      <c r="X26" s="3" t="n"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -4293,7 +4310,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4358
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
@@ -4317,7 +4334,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1312
+          <t xml:space="preserve">0122
 </t>
         </is>
       </c>
@@ -4329,7 +4346,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4347,19 +4364,19 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -4375,7 +4392,7 @@
 </t>
         </is>
       </c>
-      <c r="Q27" s="8" t="inlineStr">
+      <c r="Q27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -4393,14 +4410,18 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="3" t="n"/>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
+          <t>30</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
@@ -4463,7 +4484,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4481,7 +4502,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4505,7 +4526,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4517,7 +4538,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -4541,19 +4562,19 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -4602,7 +4623,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">3097
 </t>
         </is>
       </c>
@@ -4614,91 +4635,96 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -4708,21 +4734,21 @@
 </t>
         </is>
       </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -4753,7 +4779,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15699
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -4777,13 +4803,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6459
+          <t xml:space="preserve">449
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">624
 </t>
         </is>
       </c>
@@ -4795,19 +4821,19 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">76 9
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">749
 </t>
         </is>
       </c>
@@ -4819,14 +4845,13 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="P30" s="3" t="n"/>
@@ -4844,7 +4869,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
@@ -4868,25 +4893,25 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8249
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942280
+          <t xml:space="preserve">94280
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -4911,11 +4936,11 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
@@ -4939,9 +4964,9 @@
 </t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4951,12 +4976,7 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">150
@@ -4965,27 +4985,37 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">604
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">199
 </t>
         </is>
       </c>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16441
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n"/>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
@@ -4997,19 +5027,19 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92116
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">011
+</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17 0
 </t>
         </is>
       </c>
@@ -5019,7 +5049,12 @@
 </t>
         </is>
       </c>
-      <c r="X31" s="3" t="n"/>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">950
@@ -5028,7 +5063,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -5051,68 +5086,69 @@
 </t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>291</t>
+          <t xml:space="preserve">391
+</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5130,34 +5166,24 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
+      <c r="U32" s="3" t="n"/>
       <c r="V32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">166
@@ -5172,19 +5198,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -5221,7 +5247,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
@@ -5239,13 +5265,13 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5257,19 +5283,19 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">601
+          <t xml:space="preserve">91619
 </t>
         </is>
       </c>
@@ -5299,23 +5325,23 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
@@ -5329,19 +5355,19 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">28809
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5364,15 +5390,15 @@
 </t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5719
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -5384,11 +5410,11 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">142
 </t>
@@ -5402,13 +5428,13 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">023
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5418,7 +5444,12 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="3" t="n"/>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
@@ -5427,7 +5458,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5439,7 +5470,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5451,13 +5482,13 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
@@ -5473,7 +5504,7 @@
 </t>
         </is>
       </c>
-      <c r="W34" s="3" t="inlineStr">
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">152
 </t>
@@ -5487,7 +5518,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">1900
 </t>
         </is>
       </c>
@@ -5512,17 +5543,17 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">121
 </t>
@@ -5540,7 +5571,7 @@
 </t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
@@ -5570,13 +5601,18 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n"/>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -5585,11 +5621,11 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
@@ -5601,15 +5637,15 @@
 </t>
         </is>
       </c>
-      <c r="S35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 1 9
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
@@ -5619,13 +5655,13 @@
 </t>
         </is>
       </c>
-      <c r="V35" s="8" t="inlineStr">
+      <c r="V35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="W35" s="3" t="inlineStr">
+      <c r="W35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">165
 </t>
@@ -5633,19 +5669,19 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
@@ -5674,13 +5710,13 @@
 </t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">138
 </t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">195
 </t>
@@ -5688,13 +5724,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -5716,7 +5752,7 @@
 </t>
         </is>
       </c>
-      <c r="L36" s="8" t="inlineStr">
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
@@ -5724,19 +5760,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -5746,9 +5782,9 @@
 </t>
         </is>
       </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -5766,13 +5802,13 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5796,13 +5832,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5827,67 +5863,67 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">3523
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">5079
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -5899,7 +5935,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5911,7 +5947,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">599
 </t>
         </is>
       </c>
@@ -5923,7 +5959,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38019
+          <t xml:space="preserve">3809
 </t>
         </is>
       </c>
@@ -5935,7 +5971,7 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">700
 </t>
         </is>
       </c>
@@ -5953,16 +5989,11 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4222
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4298
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="n"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5984,7 +6015,8 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>837</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -5999,33 +6031,33 @@
 </t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0351
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1702
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -6035,7 +6067,7 @@
 </t>
         </is>
       </c>
-      <c r="M38" s="8" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">135
 </t>
@@ -6043,7 +6075,8 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -6054,7 +6087,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02 4
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
@@ -6064,13 +6097,13 @@
 </t>
         </is>
       </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="S38" s="8" t="inlineStr">
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
@@ -6084,11 +6117,11 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6 1
-</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -6100,7 +6133,7 @@
 </t>
         </is>
       </c>
-      <c r="X38" s="3" t="inlineStr">
+      <c r="X38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
@@ -6108,13 +6141,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -6133,7 +6166,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6244
+          <t xml:space="preserve">6243
 </t>
         </is>
       </c>
@@ -6143,9 +6176,9 @@
 </t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6169,24 +6202,25 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -6198,13 +6232,14 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>910</t>
+          <t xml:space="preserve">910
+</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6215,19 +6250,19 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6243,21 +6278,21 @@
 </t>
         </is>
       </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="W39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">625
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">715
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6269,7 +6304,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -6300,7 +6335,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -6310,15 +6345,16 @@
 </t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">653
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">153
+</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -6365,7 +6401,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6383,13 +6419,13 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">19488
 </t>
         </is>
       </c>
@@ -6401,7 +6437,7 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6425,7 +6461,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6444,7 +6480,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6993
+          <t xml:space="preserve">6443
 </t>
         </is>
       </c>
@@ -6456,13 +6492,13 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -6473,15 +6509,10 @@
         </is>
       </c>
       <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
+      <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -6491,27 +6522,27 @@
 </t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">015
+</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -6527,57 +6558,57 @@
 </t>
         </is>
       </c>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">722
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9470
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6417
-</t>
-        </is>
-      </c>
-      <c r="W41" s="8" t="inlineStr">
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
+      <c r="X41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6606,33 +6637,33 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">709
 </t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -6644,31 +6675,31 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6678,9 +6709,9 @@
 </t>
         </is>
       </c>
-      <c r="Q42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">617
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -6690,42 +6721,37 @@
 </t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
+      <c r="S42" s="3" t="n"/>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
+      <c r="X42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">610
@@ -6734,7 +6760,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6753,7 +6779,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50494
+          <t xml:space="preserve">6044
 </t>
         </is>
       </c>
@@ -6763,16 +6789,21 @@
 </t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
         </is>
       </c>
-      <c r="F43" s="3" t="n"/>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 279
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6800,33 +6831,33 @@
 </t>
         </is>
       </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -6844,25 +6875,24 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -6872,21 +6902,21 @@
 </t>
         </is>
       </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+      <c r="X43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">2392
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2109
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
@@ -6953,7 +6983,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
@@ -6971,7 +7001,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
+          <t xml:space="preserve">772
 </t>
         </is>
       </c>
@@ -6989,43 +7019,42 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">1559
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">1619
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">94980
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -7043,19 +7072,20 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21725
+          <t xml:space="preserve">2825
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -7066,19 +7096,19 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">106888
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3028
+          <t xml:space="preserve">23028
 </t>
         </is>
       </c>
@@ -7115,19 +7145,19 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
+          <t xml:space="preserve">1017
 </t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10154
+          <t xml:space="preserve">513
 </t>
         </is>
       </c>
@@ -7145,43 +7175,43 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11119
 </t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">12138
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
-        </is>
-      </c>
-      <c r="N46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="P46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -7191,37 +7221,42 @@
 </t>
         </is>
       </c>
-      <c r="R46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3654
-</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18416
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n"/>
+          <t xml:space="preserve">654
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
@@ -7230,13 +7265,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,146 +737,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
-</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>199</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -894,146 +870,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
-</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="W5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1051,141 +1003,118 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
-</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>116</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">942
-</t>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1203,146 +1132,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1360,146 +1265,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
-</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>196</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1517,14 +1398,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
-</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1534,128 +1413,107 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>841</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
-</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8918
-</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>955</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1673,146 +1531,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>11001</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1914
-</t>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1830,146 +1664,122 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3246
-</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">753
-</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">553
-</t>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>153</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>156</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">023
-</t>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>223</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12204
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1586
-</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>181</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1987,146 +1797,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2810
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2144,92 +1930,77 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
-</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>116</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -2239,50 +2010,42 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2300,146 +2063,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3319
-</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
-</t>
+          <t>711</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2457,146 +2196,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
-</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2614,68 +2329,57 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23069
-</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">652
-</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">669
-</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2685,69 +2389,58 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
-</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>998</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2765,146 +2458,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4614
-</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412
-</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">014
-</t>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2922,146 +2591,122 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
-</t>
+          <t>680</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3079,74 +2724,62 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>106</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3156,68 +2789,57 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">794
-</t>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3235,74 +2857,62 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1254
-</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -3312,68 +2922,57 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 0
-</t>
+          <t>12 0</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3391,146 +2990,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
-</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411
-</t>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
-</t>
+          <t>809</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9181
-</t>
+          <t>981</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3548,146 +3123,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3705,38 +3256,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20894
-</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
-</t>
+          <t>539</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3746,26 +3291,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -3775,69 +3316,58 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
-</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3855,141 +3385,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4179
-</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>108</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>139</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4007,128 +3518,107 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
-</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
@@ -4138,14 +3628,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4163,135 +3651,113 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283
-</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="X26" s="3" t="n"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z26" s="3" t="n"/>
@@ -4310,110 +3776,92 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0122
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">735
-</t>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -4421,34 +3869,29 @@
           <t>30</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4466,146 +3909,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
-</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="R28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4623,68 +4042,57 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3097
-</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>122</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -4694,74 +4102,62 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358
-</t>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4779,74 +4175,62 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">449
-</t>
+          <t>449</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76 9
-</t>
+          <t>76 9</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4857,62 +4241,52 @@
       <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>994</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94280
-</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4930,141 +4304,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140
-</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">878
-</t>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 0
-</t>
+          <t>17 0</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5082,136 +4433,114 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3642
-</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">819
-</t>
+          <t>3646</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">716
-</t>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>115</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>148</t>
         </is>
       </c>
       <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U32" s="3" t="n"/>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="W32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>162</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5229,146 +4558,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>115</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91619
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>161</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="W33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28809
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5386,146 +4691,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114
-</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 1
-</t>
+          <t>115 0</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="W34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>152</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5543,146 +4824,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>181</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1 9
-</t>
+          <t>8 9</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">608
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5700,146 +4957,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5857,140 +5090,117 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20782
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3523
-</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079
-</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>771</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
-</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
-</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
-</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
-</t>
+          <t>700</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="Z37" s="3" t="n"/>
@@ -6009,146 +5219,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>137</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6166,146 +5352,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">715
-</t>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6323,146 +5485,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
-</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">653
-</t>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>163</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6480,136 +5618,114 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6443
-</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">015
-</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>125</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
-</t>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>153</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6627,141 +5743,118 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
-</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">709
-</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>132</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S42" s="3" t="n"/>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6779,98 +5872,82 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
-</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -6880,44 +5957,37 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>214</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="X43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1209
-</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>121</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6935,8 +6005,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6977,44 +6046,37 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
-</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
-</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
-</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -7024,98 +6086,82 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1559
-</t>
+          <t>559</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94980
-</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825
-</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
-</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106888
-</t>
+          <t>608</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028
-</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7133,146 +6179,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
-</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1017
-</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">513
-</t>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>155</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">11119
-</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111111110</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>111</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">654
-</t>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -852,7 +843,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -1079,12 +1070,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>675</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1192,7 +1183,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1320,12 +1311,12 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1458,7 +1449,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1478,12 +1469,12 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1508,7 +1499,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -1569,9 +1560,9 @@
           <t>19</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>11001</t>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>0101</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1591,7 +1582,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>286</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1641,7 +1632,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1674,7 +1665,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1709,7 +1700,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1744,7 +1735,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1769,7 +1760,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1797,7 +1788,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1852,17 +1843,17 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1882,7 +1873,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1995,7 +1986,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2040,7 +2031,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2113,12 +2104,12 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>143</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2216,7 +2207,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -2226,7 +2217,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2389,7 +2380,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P16" s="3" t="n"/>
@@ -2410,7 +2401,7 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -2430,12 +2421,12 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>993</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2458,12 +2449,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2646,12 +2637,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2724,7 +2715,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2764,7 +2755,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -2774,12 +2765,12 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2857,7 +2848,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2912,7 +2903,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2995,7 +2986,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3095,12 +3086,12 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3178,7 +3169,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3256,7 +3247,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3291,7 +3282,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>154</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3362,7 +3353,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3385,7 +3376,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3425,12 +3416,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>141</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3440,7 +3431,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>262</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3470,7 +3461,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>656</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3500,7 +3491,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3518,7 +3509,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3573,7 +3564,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3608,12 +3599,12 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3671,7 +3662,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>71 2</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3706,7 +3697,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3776,7 +3767,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3881,7 +3872,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -3989,12 +3980,12 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
@@ -4082,12 +4073,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>131</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4122,7 +4113,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -4142,7 +4133,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
@@ -4180,7 +4171,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1168 2</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4230,7 +4221,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4251,12 +4242,12 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4281,7 +4272,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4309,7 +4300,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4319,12 +4310,12 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>904</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4350,12 +4341,12 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>149 1</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4385,17 +4376,17 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>916</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>17 0</t>
+          <t>17 04</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4438,7 +4429,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4448,7 +4439,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1815 0</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4473,17 +4464,17 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>323</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>219</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -4493,7 +4484,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4540,7 +4531,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -4558,7 +4549,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4648,7 +4639,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4668,12 +4659,12 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -4736,12 +4727,12 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>115 0</t>
+          <t>115 00</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -4751,7 +4742,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>291</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4776,12 +4767,12 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>960</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
@@ -4806,7 +4797,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4824,7 +4815,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4904,7 +4895,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>8 9</t>
+          <t>2 7 9</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -4957,7 +4948,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5017,7 +5008,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -5042,7 +5033,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>541</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5090,7 +5081,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5110,7 +5101,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5155,7 +5146,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5175,7 +5166,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3809 1</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5185,7 +5176,7 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>900</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -5219,7 +5210,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -5259,7 +5250,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5352,7 +5343,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -5412,7 +5403,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5422,7 +5413,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
@@ -5432,7 +5423,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>06</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -5485,7 +5476,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5550,7 +5541,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -5565,7 +5556,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -5628,7 +5619,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5665,12 +5656,12 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5753,7 +5744,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -5957,12 +5948,12 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>322</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>189</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
@@ -6046,7 +6037,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6101,12 +6092,12 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>659</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>260</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6161,7 +6152,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6217,9 +6208,9 @@
           <t>55</t>
         </is>
       </c>
-      <c r="K46" s="8" t="inlineStr">
-        <is>
-          <t>111111110</t>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6244,7 +6235,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6264,7 +6255,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6274,7 +6265,7 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
@@ -1070,7 +1070,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>895</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>0101</t>
+          <t>210</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>511</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>301</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>998</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>561</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>12 0</t>
+          <t>02 0</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>508</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>173</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>71 2</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>139</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1168 2</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -4376,17 +4376,17 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>856</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>17 04</t>
+          <t>17 00</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>1815 0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4469,22 +4469,22 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>181</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>211</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>115 00</t>
+          <t>15 0</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>900</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>2 7 9</t>
+          <t>2 1 2 8</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>581</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>078</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>3809 1</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>488</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6087,17 +6087,17 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>554</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>654</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>505</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
